--- a/config/anomaly-arbitration/data/AnomalyArbitration.xlsx
+++ b/config/anomaly-arbitration/data/AnomalyArbitration.xlsx
@@ -576,9 +576,9 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" style="5" min="8" max="8"/>
     <col width="20" customWidth="1" style="5" min="9" max="9"/>
-    <col width="23" customWidth="1" style="5" min="10" max="10"/>
-    <col width="25" customWidth="1" style="5" min="11" max="11"/>
-    <col width="26" customWidth="1" style="5" min="12" max="12"/>
+    <col width="24" customWidth="1" style="5" min="10" max="10"/>
+    <col width="26" customWidth="1" style="5" min="11" max="11"/>
+    <col width="27" customWidth="1" style="5" min="12" max="12"/>
     <col width="60" customWidth="1" style="5" min="13" max="13"/>
     <col width="60" customWidth="1" style="5" min="14" max="14"/>
     <col width="43" customWidth="1" style="5" min="15" max="16"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAProfiles</t>
+          <t>ArbProfiles</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>5d70693774e187ee</t>
+          <t>8e41c1906287fe2d</t>
         </is>
       </c>
     </row>
@@ -855,22 +855,22 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -1162,16 +1162,16 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="Q8:Q1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -1193,7 +1193,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="43" customWidth="1" style="5" min="4" max="8"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="31" customWidth="1" min="6" max="6"/>
@@ -1201,9 +1201,9 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" style="5" min="9" max="9"/>
     <col width="20" customWidth="1" style="5" min="10" max="10"/>
-    <col width="23" customWidth="1" style="5" min="11" max="11"/>
+    <col width="24" customWidth="1" style="5" min="11" max="11"/>
     <col width="29" customWidth="1" style="5" min="12" max="12"/>
-    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="13" max="13"/>
     <col width="56" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAKingProtection</t>
+          <t>ArbKingProtection</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>76e01b96f0266e66</t>
+          <t>500af8a16426580c</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1484,22 +1484,22 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -2007,16 +2007,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="Q8:Q1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -2038,7 +2038,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="32" customWidth="1" style="5" min="4" max="5"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" style="5" min="6" max="6"/>
@@ -2047,9 +2047,9 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="31" customWidth="1" style="5" min="10" max="10"/>
     <col width="20" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
     <col width="29" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAClocks</t>
+          <t>ArbClocks</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>6fae731299790b03</t>
+          <t>72845d73c8f623db</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -3299,16 +3299,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -3330,7 +3330,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="25" customWidth="1" style="5" min="4" max="4"/>
     <col width="19" customWidth="1" style="5" min="5" max="5"/>
     <col width="15" customWidth="1" style="5" min="6" max="9"/>
@@ -3338,10 +3338,10 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="31" customWidth="1" style="5" min="10" max="10"/>
-    <col width="19" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
-    <col width="25" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="20" customWidth="1" style="5" min="11" max="11"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
+    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="40" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAQuadrantOptions</t>
+          <t>ArbQuadrantOptions</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>aa248a8db4b193fe</t>
+          <t>6445cff54a147672</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -3637,22 +3637,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -4111,16 +4111,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -4142,7 +4142,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="37" customWidth="1" style="5" min="4" max="5"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" style="5" min="6" max="6"/>
@@ -4151,9 +4151,9 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="31" customWidth="1" style="5" min="10" max="10"/>
     <col width="20" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
-    <col width="25" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
+    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAQuadrantSelections</t>
+          <t>ArbQuadrantSelections</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>faad7d6eee209870</t>
+          <t>3894955cac865078</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -4449,22 +4449,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -4923,16 +4923,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -4954,7 +4954,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="20" customWidth="1" style="5" min="4" max="4"/>
     <col width="19" customWidth="1" style="5" min="5" max="5"/>
     <col width="15" customWidth="1" style="5" min="6" max="9"/>
@@ -4962,10 +4962,10 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" style="5" min="10" max="10"/>
-    <col width="19" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
-    <col width="25" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="20" customWidth="1" style="5" min="11" max="11"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
+    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="40" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AATargets</t>
+          <t>ArbTargets</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>cea580f3083e97b6</t>
+          <t>f5e1a193a88bfe9a</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -5261,22 +5261,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -6055,16 +6055,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -6086,7 +6086,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="34" customWidth="1" style="5" min="4" max="5"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" style="5" min="6" max="6"/>
@@ -6095,9 +6095,9 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="32" customWidth="1" style="5" min="10" max="10"/>
     <col width="20" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
-    <col width="25" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
+    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAObjectives</t>
+          <t>ArbObjectives</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>6d2e276da7738fdd</t>
+          <t>99b25f3f6c72a26f</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -6393,22 +6393,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -6867,16 +6867,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -6898,7 +6898,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="18" customWidth="1" style="5" min="3" max="3"/>
+    <col width="19" customWidth="1" style="5" min="3" max="3"/>
     <col width="26" customWidth="1" style="5" min="4" max="5"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" style="5" min="6" max="6"/>
@@ -6907,9 +6907,9 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" style="5" min="10" max="10"/>
     <col width="20" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
-    <col width="25" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
+    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAStageResults</t>
+          <t>ArbStageResults</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>d03cc1d19afbb12b</t>
+          <t>945c2e477edd7b17</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAStages.id&gt;</t>
+          <t>ref&lt;ArbStages.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -7205,22 +7205,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -7839,16 +7839,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -7870,7 +7870,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="44" customWidth="1" style="5" min="4" max="5"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" style="5" min="6" max="6"/>
@@ -7879,9 +7879,9 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" style="5" min="10" max="10"/>
     <col width="20" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
     <col width="29" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="55" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAAggregations</t>
+          <t>ArbAggregations</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>331f358e56d29983</t>
+          <t>c7c85c9f284a79df</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -8177,22 +8177,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -8811,16 +8811,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -8842,7 +8842,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="15" customWidth="1" style="5" min="4" max="4"/>
     <col width="17" customWidth="1" style="5" min="5" max="5"/>
     <col width="25" customWidth="1" style="5" min="6" max="8"/>
@@ -8850,9 +8850,9 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="43" customWidth="1" style="5" min="9" max="9"/>
     <col width="20" customWidth="1" style="5" min="10" max="10"/>
-    <col width="23" customWidth="1" style="5" min="11" max="11"/>
+    <col width="24" customWidth="1" style="5" min="11" max="11"/>
     <col width="29" customWidth="1" style="5" min="12" max="12"/>
-    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="13" max="13"/>
     <col width="60" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="40" customWidth="1" style="5" min="16" max="17"/>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAPeriods</t>
+          <t>ArbPeriods</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>223cc75d080562d7</t>
+          <t>de07eb78dcf1943b</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -9144,22 +9144,22 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -9461,16 +9461,16 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -9492,20 +9492,20 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="19" customWidth="1" style="5" min="3" max="3"/>
+    <col width="20" customWidth="1" style="5" min="3" max="3"/>
     <col width="19" customWidth="1" style="5" min="4" max="4"/>
     <col width="17" customWidth="1" style="5" min="5" max="5"/>
     <col width="13" customWidth="1" style="5" min="6" max="6"/>
-    <col width="19" customWidth="1" style="5" min="7" max="7"/>
-    <col width="20" customWidth="1" style="5" min="8" max="8"/>
+    <col width="20" customWidth="1" style="5" min="7" max="7"/>
+    <col width="21" customWidth="1" style="5" min="8" max="8"/>
     <col width="23" customWidth="1" style="5" min="9" max="11"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="38" customWidth="1" style="5" min="12" max="12"/>
     <col width="20" customWidth="1" style="5" min="13" max="13"/>
-    <col width="23" customWidth="1" style="5" min="14" max="14"/>
+    <col width="24" customWidth="1" style="5" min="14" max="14"/>
     <col width="29" customWidth="1" style="5" min="15" max="15"/>
-    <col width="26" customWidth="1" style="5" min="16" max="16"/>
+    <col width="27" customWidth="1" style="5" min="16" max="16"/>
     <col width="60" customWidth="1" style="5" min="17" max="17"/>
     <col width="60" customWidth="1" style="5" min="18" max="18"/>
     <col width="40" customWidth="1" style="5" min="19" max="20"/>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAStages</t>
+          <t>ArbStages</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>6f4c5caac5fbb95b</t>
+          <t>8ffccf69075880d3</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAPeriods.id&gt;</t>
+          <t>ref&lt;ArbPeriods.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -9812,12 +9812,12 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAStageKind&gt;</t>
+          <t>enum&lt;ArbStageKind&gt;</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AADifficulty&gt;</t>
+          <t>enum&lt;ArbDifficulty&gt;</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -9842,22 +9842,22 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="Q4" s="5" t="inlineStr">
@@ -10581,22 +10581,22 @@
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
-    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Knight, King" promptTitle="AAStageKind enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="G8:G1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Knight, King" promptTitle="ArbStageKind enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Knight,King"</formula1>
     </dataValidation>
-    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Normal, Plight" promptTitle="AADifficulty enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="H8:H1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Normal, Plight" promptTitle="ArbDifficulty enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Normal,Plight"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="O8:O1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="P8:P1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="P8:P1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="U8:U1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -10618,16 +10618,16 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="31" customWidth="1" style="5" min="4" max="7"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" style="5" min="8" max="8"/>
     <col width="20" customWidth="1" style="5" min="9" max="9"/>
-    <col width="23" customWidth="1" style="5" min="10" max="10"/>
-    <col width="25" customWidth="1" style="5" min="11" max="11"/>
-    <col width="26" customWidth="1" style="5" min="12" max="12"/>
+    <col width="24" customWidth="1" style="5" min="10" max="10"/>
+    <col width="26" customWidth="1" style="5" min="11" max="11"/>
+    <col width="27" customWidth="1" style="5" min="12" max="12"/>
     <col width="41" customWidth="1" style="5" min="13" max="13"/>
     <col width="60" customWidth="1" style="5" min="14" max="14"/>
     <col width="40" customWidth="1" style="5" min="15" max="16"/>
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AATerminalOutcomes</t>
+          <t>ArbTerminalOutcomes</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>5bffe88df6082748</t>
+          <t>f9d1cb1fa03f3370</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -10904,22 +10904,22 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -11436,16 +11436,16 @@
       <formula1>1</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="I8:I1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="Q8:Q1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -11467,7 +11467,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="57" customWidth="1" style="5" min="4" max="8"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="41" customWidth="1" min="6" max="6"/>
@@ -11475,9 +11475,9 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="41" customWidth="1" style="5" min="9" max="9"/>
     <col width="20" customWidth="1" style="5" min="10" max="10"/>
-    <col width="23" customWidth="1" style="5" min="11" max="11"/>
-    <col width="25" customWidth="1" style="5" min="12" max="12"/>
-    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="24" customWidth="1" style="5" min="11" max="11"/>
+    <col width="26" customWidth="1" style="5" min="12" max="12"/>
+    <col width="27" customWidth="1" style="5" min="13" max="13"/>
     <col width="59" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="40" customWidth="1" style="5" min="16" max="17"/>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAParticipantPolicies</t>
+          <t>ArbParticipantPolicies</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>e677d36fd26625cb</t>
+          <t>24185a86735a18a9</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11734,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -11769,22 +11769,22 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -12328,16 +12328,16 @@
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -12359,8 +12359,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
-    <col width="18" customWidth="1" style="5" min="4" max="4"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
+    <col width="19" customWidth="1" style="5" min="4" max="4"/>
     <col width="20" customWidth="1" style="5" min="5" max="9"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -12368,9 +12368,9 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" style="5" min="10" max="10"/>
     <col width="20" customWidth="1" style="5" min="11" max="11"/>
-    <col width="23" customWidth="1" style="5" min="12" max="12"/>
-    <col width="25" customWidth="1" style="5" min="13" max="13"/>
-    <col width="26" customWidth="1" style="5" min="14" max="14"/>
+    <col width="24" customWidth="1" style="5" min="12" max="12"/>
+    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="14" max="14"/>
     <col width="46" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
     <col width="40" customWidth="1" style="5" min="17" max="18"/>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AATeamSlots</t>
+          <t>ArbTeamSlots</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>5cfa3d3cd764b78f</t>
+          <t>5f629bd6046c6c98</t>
         </is>
       </c>
     </row>
@@ -12637,12 +12637,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAStages.id&gt;</t>
+          <t>ref&lt;ArbStages.id&gt;</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12677,22 +12677,22 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -13172,16 +13172,16 @@
       <formula1>1</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="N8:N1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="S8:S1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -13203,7 +13203,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="50" customWidth="1" style="5" min="4" max="8"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
@@ -13211,9 +13211,9 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="36" customWidth="1" style="5" min="9" max="9"/>
     <col width="20" customWidth="1" style="5" min="10" max="10"/>
-    <col width="23" customWidth="1" style="5" min="11" max="11"/>
-    <col width="25" customWidth="1" style="5" min="12" max="12"/>
-    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="24" customWidth="1" style="5" min="11" max="11"/>
+    <col width="26" customWidth="1" style="5" min="12" max="12"/>
+    <col width="27" customWidth="1" style="5" min="13" max="13"/>
     <col width="60" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="40" customWidth="1" style="5" min="16" max="17"/>
@@ -13229,7 +13229,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AALoadoutRecords</t>
+          <t>ArbLoadoutRecords</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>ca818c3e9587d3f0</t>
+          <t>8f962f87d981d726</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -13505,22 +13505,22 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -13984,16 +13984,16 @@
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -14015,7 +14015,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="46" customWidth="1" style="5" min="4" max="8"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
@@ -14023,9 +14023,9 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="36" customWidth="1" style="5" min="9" max="9"/>
     <col width="20" customWidth="1" style="5" min="10" max="10"/>
-    <col width="23" customWidth="1" style="5" min="11" max="11"/>
-    <col width="25" customWidth="1" style="5" min="12" max="12"/>
-    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="24" customWidth="1" style="5" min="11" max="11"/>
+    <col width="26" customWidth="1" style="5" min="12" max="12"/>
+    <col width="27" customWidth="1" style="5" min="13" max="13"/>
     <col width="57" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="40" customWidth="1" style="5" min="16" max="17"/>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAProgressRecords</t>
+          <t>ArbProgressRecords</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -14081,7 +14081,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>d1dcd76b7da2d723</t>
+          <t>841d6697256ce8d5</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -14317,22 +14317,22 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -15036,16 +15036,16 @@
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="R8:R1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
@@ -15067,7 +15067,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" style="5" min="2" max="2"/>
-    <col width="20" customWidth="1" style="5" min="3" max="3"/>
+    <col width="21" customWidth="1" style="5" min="3" max="3"/>
     <col width="19" customWidth="1" style="5" min="4" max="8"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -15075,9 +15075,9 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" style="5" min="9" max="9"/>
     <col width="20" customWidth="1" style="5" min="10" max="10"/>
-    <col width="23" customWidth="1" style="5" min="11" max="11"/>
+    <col width="24" customWidth="1" style="5" min="11" max="11"/>
     <col width="29" customWidth="1" style="5" min="12" max="12"/>
-    <col width="26" customWidth="1" style="5" min="13" max="13"/>
+    <col width="27" customWidth="1" style="5" min="13" max="13"/>
     <col width="42" customWidth="1" style="5" min="14" max="14"/>
     <col width="60" customWidth="1" style="5" min="15" max="15"/>
     <col width="60" customWidth="1" style="5" min="16" max="16"/>
@@ -15092,7 +15092,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>AAKingStates</t>
+          <t>ArbKingStates</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>6eb8618cc70e8adb</t>
+          <t>05b940e2f1ce7343</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>ref&lt;AAProfiles.id&gt;</t>
+          <t>ref&lt;ArbProfiles.id&gt;</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -15358,22 +15358,22 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAOwnership&gt;</t>
+          <t>enum&lt;ArbOwnership&gt;</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AACoverageState&gt;</t>
+          <t>enum&lt;ArbCoverageState&gt;</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAEvidenceQuality&gt;</t>
+          <t>enum&lt;ArbEvidenceQuality&gt;</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enum&lt;AAMechanismQuality&gt;</t>
+          <t>enum&lt;ArbMechanismQuality&gt;</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -15731,16 +15731,16 @@
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AA, Shared" promptTitle="AAOwnership enum" prompt="Select a value from the dropdown." type="list">
-      <formula1>"AA,Shared"</formula1>
+    <dataValidation sqref="J8:J1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: AnomalyArbitration, Shared" promptTitle="ArbOwnership enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"AnomalyArbitration,Shared"</formula1>
     </dataValidation>
-    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="AACoverageState enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="K8:K1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Cataloged, Researched, DataReady, Blocked" promptTitle="ArbCoverageState enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"Cataloged,Researched,DataReady,Blocked"</formula1>
     </dataValidation>
-    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="AAEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="L8:L1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactStructured, ExactPublicText, Observed, ApproximateFromReleasedText, ProjectPolicy" promptTitle="ArbEvidenceQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactStructured,ExactPublicText,Observed,ApproximateFromReleasedText,ProjectPolicy"</formula1>
     </dataValidation>
-    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="AAMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
+    <dataValidation sqref="M8:M1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: ExactProgram, ExactRelationship, ObservedBehavior, IdentityCrossCheck, PolicyBoundary, ContextOnly" promptTitle="ArbMechanismQuality enum" prompt="Select a value from the dropdown." type="list">
       <formula1>"ExactProgram,ExactRelationship,ObservedBehavior,IdentityCrossCheck,PolicyBoundary,ContextOnly"</formula1>
     </dataValidation>
     <dataValidation sqref="Q8:Q1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid boolean value" error="Value must be true or false." promptTitle="Boolean" prompt="Select true or false." type="list">
